--- a/outputs/Коммерческое_предложение.xlsx
+++ b/outputs/Коммерческое_предложение.xlsx
@@ -555,10 +555,10 @@
         <v>6962</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2763914</v>
+        <v>2903154</v>
       </c>
     </row>
     <row r="7">
@@ -574,10 +574,10 @@
         <v>3287</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1436419</v>
+        <v>1508733</v>
       </c>
     </row>
     <row r="8">
@@ -593,10 +593,10 @@
         <v>2187</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>964467</v>
+        <v>1012581</v>
       </c>
     </row>
     <row r="9">
@@ -612,10 +612,10 @@
         <v>592</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1097</v>
+        <v>1152</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>649424</v>
+        <v>681984</v>
       </c>
     </row>
     <row r="10">
@@ -631,10 +631,10 @@
         <v>446</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>814</v>
+        <v>855</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>363044</v>
+        <v>381330</v>
       </c>
     </row>
     <row r="11">
@@ -650,10 +650,10 @@
         <v>1124</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>328208</v>
+        <v>343944</v>
       </c>
     </row>
     <row r="12">
@@ -669,10 +669,10 @@
         <v>525</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>605</v>
+        <v>635</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>317625</v>
+        <v>333375</v>
       </c>
     </row>
     <row r="13">
@@ -688,10 +688,10 @@
         <v>352</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>281600</v>
+        <v>295680</v>
       </c>
     </row>
     <row r="14">
@@ -707,10 +707,10 @@
         <v>504</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>213696</v>
+        <v>224280</v>
       </c>
     </row>
     <row r="15">
@@ -726,10 +726,10 @@
         <v>664</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>138112</v>
+        <v>144752</v>
       </c>
     </row>
     <row r="16">
@@ -745,10 +745,10 @@
         <v>682</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>137082</v>
+        <v>143902</v>
       </c>
     </row>
     <row r="17">
@@ -764,10 +764,10 @@
         <v>112</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>106400</v>
+        <v>111776</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +783,10 @@
         <v>190</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>101840</v>
+        <v>106780</v>
       </c>
     </row>
     <row r="19">
@@ -802,10 +802,10 @@
         <v>454</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>91254</v>
+        <v>95794</v>
       </c>
     </row>
     <row r="20">
@@ -821,10 +821,10 @@
         <v>165</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>87780</v>
+        <v>92235</v>
       </c>
     </row>
     <row r="21">
@@ -840,10 +840,10 @@
         <v>319</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>84854</v>
+        <v>89320</v>
       </c>
     </row>
     <row r="22">
@@ -859,10 +859,10 @@
         <v>103</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>736</v>
+        <v>773</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>75808</v>
+        <v>79619</v>
       </c>
     </row>
     <row r="23">
@@ -878,10 +878,10 @@
         <v>95</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>794</v>
+        <v>834</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>75430</v>
+        <v>79230</v>
       </c>
     </row>
     <row r="24">
@@ -897,10 +897,10 @@
         <v>185</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>69930</v>
+        <v>73445</v>
       </c>
     </row>
     <row r="25">
@@ -916,10 +916,10 @@
         <v>55</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1163</v>
+        <v>1221</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>63965</v>
+        <v>67155</v>
       </c>
     </row>
     <row r="26">
@@ -935,10 +935,10 @@
         <v>289</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>58089</v>
+        <v>60979</v>
       </c>
     </row>
     <row r="27">
@@ -954,10 +954,10 @@
         <v>76</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>757</v>
+        <v>795</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>57532</v>
+        <v>60420</v>
       </c>
     </row>
     <row r="28">
@@ -973,10 +973,10 @@
         <v>313</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>55401</v>
+        <v>58218</v>
       </c>
     </row>
     <row r="29">
@@ -992,10 +992,10 @@
         <v>292</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>48472</v>
+        <v>50808</v>
       </c>
     </row>
     <row r="30">
@@ -1011,10 +1011,10 @@
         <v>350</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>41650</v>
+        <v>43750</v>
       </c>
     </row>
     <row r="31">
@@ -1030,10 +1030,10 @@
         <v>33</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1202</v>
+        <v>1262</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>39666</v>
+        <v>41646</v>
       </c>
     </row>
     <row r="32">
@@ -1049,10 +1049,10 @@
         <v>60</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>650</v>
+        <v>683</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>39000</v>
+        <v>40980</v>
       </c>
     </row>
     <row r="33">
@@ -1068,10 +1068,10 @@
         <v>126</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>33642</v>
+        <v>35406</v>
       </c>
     </row>
     <row r="34">
@@ -1087,10 +1087,10 @@
         <v>428</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>33384</v>
+        <v>35096</v>
       </c>
     </row>
     <row r="35">
@@ -1106,10 +1106,10 @@
         <v>158</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>31916</v>
+        <v>33654</v>
       </c>
     </row>
     <row r="36">
@@ -1125,10 +1125,10 @@
         <v>35</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>840</v>
+        <v>882</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>29400</v>
+        <v>30870</v>
       </c>
     </row>
     <row r="37">
@@ -1144,10 +1144,10 @@
         <v>50</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>24650</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="38">
@@ -1163,10 +1163,10 @@
         <v>170</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>24480</v>
+        <v>25670</v>
       </c>
     </row>
     <row r="39">
@@ -1182,10 +1182,10 @@
         <v>25</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>930</v>
+        <v>976</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>23250</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="40">
@@ -1201,10 +1201,10 @@
         <v>23</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>792</v>
+        <v>832</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>18216</v>
+        <v>19136</v>
       </c>
     </row>
     <row r="41">
@@ -1220,10 +1220,10 @@
         <v>55</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>16335</v>
+        <v>17160</v>
       </c>
     </row>
     <row r="42">
@@ -1239,10 +1239,10 @@
         <v>28</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>11340</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="43">
@@ -1258,10 +1258,10 @@
         <v>21</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>6783</v>
+        <v>7140</v>
       </c>
     </row>
     <row r="44">
@@ -1277,10 +1277,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>5712</v>
+        <v>5984</v>
       </c>
     </row>
     <row r="45">
@@ -1296,10 +1296,10 @@
         <v>17</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>4046</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="46">
@@ -1315,10 +1315,10 @@
         <v>12</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2940</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="47">
@@ -1334,10 +1334,10 @@
         <v>5</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1730</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="48">
@@ -1353,10 +1353,10 @@
         <v>1</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>902</v>
+        <v>947</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>902</v>
+        <v>947</v>
       </c>
     </row>
     <row r="49">
@@ -1371,13 +1371,13 @@
       </c>
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="10" t="n">
-        <v>8959388</v>
+        <v>9408232</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>Всего позиций: 43   |   Общее количество: 21,587 шт   |   Сумма предложения: 8,959,388 ₽</t>
+          <t>Всего позиций: 43   |   Общее количество: 21,587 шт   |   Сумма предложения: 9,408,232 ₽</t>
         </is>
       </c>
     </row>
